--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20231.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -85,10 +85,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
     <t>ABAD</t>
   </si>
   <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
   </si>
   <si>
     <t>MARITZA</t>
@@ -489,10 +498,10 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -501,7 +510,7 @@
         <v>31</v>
       </c>
       <c r="G2">
-        <v>91.18000000000001</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H2">
         <v>8.4</v>
@@ -515,19 +524,19 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>39</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="H3">
         <v>8.6</v>
@@ -678,10 +687,10 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2">
         <v>34</v>
@@ -701,13 +710,13 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -852,10 +861,10 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -864,7 +873,7 @@
         <v>31</v>
       </c>
       <c r="G2">
-        <v>91.18000000000001</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H2">
         <v>8.4</v>
@@ -878,19 +887,19 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>39</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="H3">
         <v>8.6</v>
@@ -1001,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1033,24 +1042,47 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920331</v>
+        <v>23330051920213</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920331</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="G2">
+      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20231.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -85,19 +85,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
     <t>ABAD</t>
   </si>
   <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
   </si>
   <si>
     <t>MARITZA</t>
@@ -498,10 +489,10 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -510,7 +501,7 @@
         <v>31</v>
       </c>
       <c r="G2">
-        <v>88.56999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H2">
         <v>8.4</v>
@@ -687,19 +678,22 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>88.23999999999999</v>
+      </c>
+      <c r="H2">
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -713,16 +707,19 @@
         <v>40</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>40</v>
       </c>
-      <c r="E3">
-        <v>40</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -736,16 +733,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>94.87</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -759,16 +759,19 @@
         <v>30</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>30</v>
       </c>
-      <c r="E5">
-        <v>30</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -802,16 +805,19 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>84</v>
+      </c>
+      <c r="H7">
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -861,19 +867,19 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>88.56999999999999</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H2">
         <v>8.4</v>
@@ -893,16 +899,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -919,16 +925,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>92.31</v>
+        <v>94.87</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -945,16 +951,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>96.67</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1000,7 +1006,7 @@
         <v>84</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1010,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1042,48 +1048,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920213</v>
+        <v>21330051920331</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
         <v>24</v>
       </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920331</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20231.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,15 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>ABAD</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
   </si>
 </sst>
 </file>
@@ -873,16 +864,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -899,16 +890,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -934,7 +925,7 @@
         <v>94.87</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -951,16 +942,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -997,13 +988,13 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G7">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="H7">
         <v>8</v>
@@ -1016,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1046,29 +1037,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920331</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20231.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20231.xlsx
@@ -584,7 +584,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -593,7 +593,13 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -773,7 +779,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -782,7 +788,13 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -962,16 +974,22 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>29</v>
+      </c>
+      <c r="G6">
+        <v>96.67</v>
+      </c>
+      <c r="H6">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20231.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20231.xlsx
@@ -885,7 +885,7 @@
         <v>94.12</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -911,7 +911,7 @@
         <v>97.5</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -937,7 +937,7 @@
         <v>94.87</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -963,7 +963,7 @@
         <v>96.67</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1015,7 +1015,7 @@
         <v>96</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20231.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20231.xlsx
@@ -885,7 +885,7 @@
         <v>94.12</v>
       </c>
       <c r="H2">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -911,7 +911,7 @@
         <v>97.5</v>
       </c>
       <c r="H3">
-        <v>9.9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -937,7 +937,7 @@
         <v>94.87</v>
       </c>
       <c r="H4">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -963,7 +963,7 @@
         <v>96.67</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1015,7 +1015,7 @@
         <v>96</v>
       </c>
       <c r="H7">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
